--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104728_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104728_W30.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0245</v>
+        <v>4.8384</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1229</v>
+        <v>2.9279</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9015</v>
+        <v>1.9106</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9923</v>
+        <v>3.9883</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3638</v>
+        <v>3.3579</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6304</v>
       </c>
       <c r="J2" t="n">
-        <v>3.378</v>
+        <v>3.3695</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2662</v>
+        <v>3.2578</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6143</v>
+        <v>0.6189</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0977</v>
+        <v>0.1002</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2594</v>
+        <v>1.0777</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8809</v>
+        <v>0.6965</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3785</v>
+        <v>0.3812</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1688</v>
+        <v>3.3204</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8853</v>
+        <v>3.9901</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7165</v>
+        <v>-0.6696</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6233</v>
+        <v>3.6218</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8212</v>
+        <v>0.8213</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8021</v>
+        <v>2.8004</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7314</v>
+        <v>4.7241</v>
       </c>
       <c r="K3" t="n">
-        <v>1.227</v>
+        <v>1.2238</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5044</v>
+        <v>3.5003</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1081</v>
+        <v>-1.1023</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4058</v>
+        <v>-0.4025</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7023</v>
+        <v>-0.6998</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2947</v>
+        <v>-0.1451</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.347</v>
+        <v>-0.2301</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0523</v>
+        <v>0.0849</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0674</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0238</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5233</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8877</v>
+        <v>-0.4229</v>
       </c>
       <c r="F4" t="n">
-        <v>1.411</v>
+        <v>1.2661</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1634</v>
+        <v>1.1627</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8798</v>
+        <v>0.8814</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2836</v>
+        <v>0.2812</v>
       </c>
       <c r="J4" t="n">
-        <v>0.103</v>
+        <v>0.0977</v>
       </c>
       <c r="K4" t="n">
-        <v>0.121</v>
+        <v>0.1207</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.018</v>
+        <v>-0.023</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0604</v>
+        <v>1.065</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7588</v>
+        <v>0.7608</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3016</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4576</v>
+        <v>-0.1405</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7635</v>
+        <v>-0.2929</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3059</v>
+        <v>0.1524</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2352</v>
+        <v>0.5843</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9232</v>
+        <v>-0.6296</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.6879</v>
+        <v>1.2139</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4485</v>
+        <v>1.2243</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7454</v>
+        <v>-0.0969</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2969</v>
+        <v>1.3213</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2808</v>
+        <v>1.7354</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8574</v>
+        <v>-0.2973</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4234</v>
+        <v>2.0327</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8323</v>
+        <v>-0.5111</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.112</v>
+        <v>0.2003</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7203</v>
+        <v>-0.7114</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9087</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7262</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6954</v>
+        <v>0.36</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0948</v>
+        <v>-0.0887</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6006</v>
+        <v>0.4487</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2738</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.2738</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1224</v>
+        <v>0.212</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7758</v>
+        <v>1.2424</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8982</v>
+        <v>-1.0304</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2792</v>
+        <v>1.3293</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7492</v>
+        <v>2.1486</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.47</v>
+        <v>-0.8192</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7862</v>
+        <v>2.9488</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7117</v>
+        <v>3.0682</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>-0.1194</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.507</v>
+        <v>-1.6194</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0375</v>
+        <v>-0.9196</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5446</v>
+        <v>-0.6998</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3631</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7262</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3631</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2064</v>
+        <v>-0.1173</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1642</v>
+        <v>-0.1326</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0421</v>
+        <v>0.0152</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0968</v>
+        <v>0.1094</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9113</v>
+        <v>3.9627</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0081</v>
+        <v>-3.8533</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2305</v>
+        <v>0.4416</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0916</v>
+        <v>1.7409</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3222</v>
+        <v>-1.2994</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7516</v>
+        <v>3.2635</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2869</v>
+        <v>2.8473</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0385</v>
+        <v>0.4162</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.521</v>
+        <v>-2.8219</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1953</v>
+        <v>-1.1064</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7163</v>
+        <v>-1.7155</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4544</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2719</v>
+        <v>-2.7316</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1337</v>
+        <v>0.5783</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.391</v>
+        <v>0.1623</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2573</v>
+        <v>0.416</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5456</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3656</v>
+        <v>-0.0349</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8361</v>
+        <v>-0.9143</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2017</v>
+        <v>0.8793</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3317</v>
+        <v>1.2739</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1519</v>
+        <v>1.7414</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8202</v>
+        <v>-0.4674</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9582</v>
+        <v>1.7734</v>
       </c>
       <c r="K8" t="n">
-        <v>3.0761</v>
+        <v>1.699</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1178</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6265</v>
+        <v>-0.4995</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9242</v>
+        <v>0.0424</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7023</v>
+        <v>-0.5419</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4544</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2719</v>
+        <v>-2.7316</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8175</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6973</v>
+        <v>0.0569</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5553</v>
+        <v>0.0439</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.142</v>
+        <v>0.013</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8472</v>
+        <v>-1.5475</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6516</v>
+        <v>-1.4232</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1956</v>
+        <v>-0.1243</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9962</v>
+        <v>-1.9957</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0112</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0052</v>
+        <v>-2.0069</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7997</v>
+        <v>-0.8051</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9332</v>
+        <v>0.9308</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7329</v>
+        <v>-1.7359</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1965</v>
+        <v>-1.1906</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9242</v>
+        <v>-0.9196</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2723</v>
+        <v>-0.271</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.987</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6247</v>
+        <v>-0.3904</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3623</v>
+        <v>-0.2995</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4114</v>
+        <v>-2.1329</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-1.4964</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6388</v>
+        <v>-0.6365</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1592</v>
+        <v>-0.7542</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8431</v>
+        <v>0.0573</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3162</v>
+        <v>-0.8115</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8293</v>
+        <v>-0.0259</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9038</v>
+        <v>0.5031</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0746</v>
+        <v>-0.529</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3299</v>
+        <v>-0.7284</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9392</v>
+        <v>-0.4458</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3907</v>
+        <v>-0.2826</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4991</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1359</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5653</v>
+        <v>0.1173</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4644</v>
+        <v>-0.1048</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1009</v>
+        <v>0.2221</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5456</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5456</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.647</v>
+        <v>-3.4761</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1473</v>
+        <v>-3.6491</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4996</v>
+        <v>0.173</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7578</v>
+        <v>-3.4412</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0563</v>
+        <v>-1.2751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8142</v>
+        <v>-2.1661</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0207</v>
+        <v>-3.5862</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5072</v>
+        <v>-1.2173</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5279</v>
+        <v>-2.3689</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7371</v>
+        <v>0.1451</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4508</v>
+        <v>-0.0578</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2863</v>
+        <v>0.2028</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3631</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0447</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3882</v>
+        <v>0.3717</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7635</v>
+        <v>-0.0629</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3753</v>
+        <v>0.4345</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7722</v>
+        <v>-3.6438</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.998</v>
+        <v>-2.0175</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2259</v>
+        <v>-1.6263</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.4407</v>
+        <v>-3.1547</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.275</v>
+        <v>-1.8411</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1656</v>
+        <v>-1.3136</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5816</v>
+        <v>-0.8326</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2149</v>
+        <v>-0.907</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3667</v>
+        <v>0.0745</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1409</v>
+        <v>-2.3221</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0601</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2011</v>
+        <v>-1.3881</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6816</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.3319</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4164</v>
+        <v>0.2296</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4946</v>
+        <v>0.1024</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0913</v>
+        <v>0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.298</v>
+        <v>-3.9022</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9022</v>
+        <v>-2.6704</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3958</v>
+        <v>-1.2318</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6862</v>
+        <v>-3.6837</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4433</v>
+        <v>-1.4418</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.2429</v>
+        <v>-2.2419</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2776</v>
+        <v>-2.28</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7371</v>
+        <v>-0.7379</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5405</v>
+        <v>-1.542</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4086</v>
+        <v>-1.4037</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7063</v>
+        <v>-0.7039</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7023</v>
+        <v>-0.6998</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5206</v>
+        <v>-0.129</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6247</v>
+        <v>-0.3904</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1041</v>
+        <v>0.2614</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.170399999999999</v>
+        <v>-4.829700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.279100000000004</v>
+        <v>-1.100299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.8912</v>
+        <v>-3.7293</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02880000000000127</v>
+        <v>0.01239999999999775</v>
       </c>
       <c r="H14" t="n">
-        <v>6.123600000000001</v>
+        <v>6.105099999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.0948</v>
+        <v>-6.092700000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>10.4803</v>
+        <v>10.3826</v>
       </c>
       <c r="K14" t="n">
-        <v>10.5571</v>
+        <v>10.4912</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.07649999999999868</v>
+        <v>-0.1082999999999996</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.4514</v>
+        <v>-10.37</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.4333</v>
+        <v>-4.385899999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.0181</v>
+        <v>-5.9841</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.039</v>
+        <v>-17.0723</v>
       </c>
       <c r="R14" t="n">
-        <v>15.903</v>
+        <v>15.9345</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3256</v>
+        <v>1.6719</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8818</v>
+        <v>-0.5605</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2073</v>
+        <v>2.2323</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.3889</v>
+        <v>-5.375900000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>6.1614</v>
+        <v>6.149900000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.5502</v>
+        <v>-11.5256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5692</v>
+        <v>4.5075</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1732</v>
+        <v>2.1331</v>
       </c>
       <c r="F15" t="n">
-        <v>0.396</v>
+        <v>2.3744</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9474</v>
+        <v>-0.2653</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4749</v>
+        <v>0.6746</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4726</v>
+        <v>-0.9399</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6423</v>
+        <v>0.2759</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2563</v>
+        <v>1.1926</v>
       </c>
       <c r="L15" t="n">
-        <v>2.386</v>
+        <v>-0.9167</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6949</v>
+        <v>-0.5412</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7814</v>
+        <v>-0.518</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0866</v>
+        <v>-0.0232</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2719</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2719</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3711</v>
+        <v>-0.3088</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4608</v>
+        <v>-0.7204</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0897</v>
+        <v>0.4116</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2507</v>
+        <v>5.9921</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3419</v>
+        <v>5.9921</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3414</v>
+        <v>4.2777</v>
       </c>
       <c r="E16" t="n">
-        <v>1.927</v>
+        <v>3.677</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4143</v>
+        <v>0.6007</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2683</v>
+        <v>2.9444</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6724</v>
+        <v>0.4714</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9407</v>
+        <v>2.473</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2857</v>
+        <v>3.6307</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1984</v>
+        <v>1.2476</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9127</v>
+        <v>2.3832</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.554</v>
+        <v>-0.6863</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.526</v>
+        <v>-0.7761</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0279</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9087</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4078</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4991</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4835</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9527</v>
+        <v>-0.0141</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4692</v>
+        <v>0.1002</v>
       </c>
       <c r="V16" t="n">
-        <v>6.0019</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>6.0019</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4918</v>
+        <v>3.564</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1702</v>
+        <v>3.6256</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3216</v>
+        <v>-0.0616</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3062</v>
+        <v>3.3075</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3636</v>
+        <v>0.3671</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9426</v>
+        <v>2.9404</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8913</v>
+        <v>4.8805</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1751</v>
+        <v>1.1721</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7161</v>
+        <v>3.7083</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5851</v>
+        <v>-1.5729</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8115</v>
+        <v>-0.805</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7736</v>
+        <v>-0.768</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6631</v>
+        <v>0.733</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.2744</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4076</v>
+        <v>1.0074</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5648</v>
+        <v>1.5793</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0038</v>
+        <v>1.9376</v>
       </c>
       <c r="F18" t="n">
-        <v>1.561</v>
+        <v>-0.3583</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8525</v>
+        <v>-1.7912</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1315</v>
+        <v>-0.3904</v>
       </c>
       <c r="I18" t="n">
-        <v>0.984</v>
+        <v>-1.4008</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6652</v>
+        <v>0.8741</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7025</v>
+        <v>1.2476</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>-0.3735</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5177</v>
+        <v>-2.6653</v>
       </c>
       <c r="N18" t="n">
-        <v>0.571</v>
+        <v>-1.638</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9467</v>
+        <v>-1.0273</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9087</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9087</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8949</v>
+        <v>-0.1743</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6691</v>
+        <v>-0.135</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2258</v>
+        <v>-0.0392</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0913</v>
+        <v>2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7999000000000001</v>
+        <v>1.2874</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4911</v>
+        <v>-0.4712</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6912</v>
+        <v>1.7586</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7866</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3892</v>
+        <v>-0.1295</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3974</v>
+        <v>0.9848</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8908</v>
+        <v>-0.6662</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2563</v>
+        <v>-0.7035</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3655</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6774</v>
+        <v>1.5215</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6455</v>
+        <v>0.574</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0319</v>
+        <v>0.9476</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3631</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4991</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9592000000000001</v>
+        <v>0.611</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6057</v>
+        <v>0.195</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3535</v>
+        <v>0.416</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1825</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3419</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4696</v>
+        <v>0.4934</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2792</v>
+        <v>0.3924</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1904</v>
+        <v>0.101</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1632</v>
+        <v>0.1635</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3847</v>
+        <v>-0.3848</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5483</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0806</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.006</v>
+        <v>0.0033</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3907</v>
+        <v>-0.3881</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4733</v>
+        <v>0.4738</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6936</v>
+        <v>-0.6701</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.347</v>
+        <v>-0.2301</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3466</v>
+        <v>-0.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2533</v>
+        <v>-0.1007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7524</v>
+        <v>0.8601</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0058</v>
+        <v>-0.9609</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9244</v>
+        <v>0.9248</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3005</v>
+        <v>-0.3014</v>
       </c>
       <c r="I21" t="n">
-        <v>1.225</v>
+        <v>1.2262</v>
       </c>
       <c r="J21" t="n">
-        <v>2.166</v>
+        <v>2.1586</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4577</v>
+        <v>1.4511</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7083</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2416</v>
+        <v>-1.2339</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7582</v>
+        <v>-1.7526</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5409</v>
+        <v>-0.3913</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2776</v>
+        <v>-0.1604</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2633</v>
+        <v>-0.2309</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5581</v>
+        <v>-0.1631</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9598</v>
+        <v>-0.7246</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4018</v>
+        <v>0.5616</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6812</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1878</v>
+        <v>-0.1868</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4933</v>
+        <v>-0.4931</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="M22" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0725</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1878</v>
+        <v>-0.1868</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2583</v>
+        <v>0.2593</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1041</v>
+        <v>0.2892</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2082</v>
+        <v>0.0278</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1041</v>
+        <v>0.2614</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5003</v>
+        <v>-2.1082</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8445</v>
+        <v>-2.5678</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3442</v>
+        <v>0.4596</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2793</v>
+        <v>-3.2731</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.7267</v>
+        <v>-3.7199</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4474</v>
+        <v>0.4468</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3146</v>
+        <v>-1.3224</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.6755</v>
+        <v>-1.6795</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3608</v>
+        <v>0.357</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9647</v>
+        <v>-1.9506</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0513</v>
+        <v>-2.0405</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0866</v>
+        <v>0.0898</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S23" t="n">
-        <v>0.416</v>
+        <v>-0.2009</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6061</v>
+        <v>-0.1072</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1901</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.381</v>
+        <v>-2.1983</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1829</v>
+        <v>-1.0674</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1981</v>
+        <v>-1.1309</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3561</v>
+        <v>-0.3529</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6867</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3329</v>
+        <v>0.3338</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0917</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.448</v>
+        <v>-0.4446</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7063</v>
+        <v>-0.7039</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2583</v>
+        <v>0.2593</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5705</v>
+        <v>-0.3902</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1388</v>
+        <v>-0.021</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4317</v>
+        <v>-0.3692</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3817</v>
+        <v>-2.8559</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4054</v>
+        <v>-0.1793</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0237</v>
+        <v>-2.6767</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.3378</v>
+        <v>-0.5108</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.949</v>
+        <v>0.1286</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6112</v>
+        <v>-0.6394</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.506</v>
+        <v>2.6295</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.5432</v>
+        <v>1.9822</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0373</v>
+        <v>0.6473</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1681</v>
+        <v>-3.1403</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4058</v>
+        <v>-1.8536</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5739</v>
+        <v>-1.2866</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8175</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4544</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7736</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3725</v>
+        <v>-0.6902</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4012</v>
+        <v>-0.268</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9918</v>
+        <v>-3.1047</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5132</v>
+        <v>-3.8862</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4787</v>
+        <v>0.7815</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5132</v>
+        <v>-1.3349</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1239</v>
+        <v>-1.9473</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6371</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>2.6404</v>
+        <v>-1.5076</v>
       </c>
       <c r="K26" t="n">
-        <v>1.9873</v>
+        <v>-1.5448</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6531</v>
+        <v>0.0372</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.1536</v>
+        <v>0.1727</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.8634</v>
+        <v>-0.4025</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.2902</v>
+        <v>0.5752</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4544</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8175</v>
+        <v>0.4553</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0924</v>
+        <v>0.0512</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0411</v>
+        <v>-0.1024</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0513</v>
+        <v>0.1535</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9318</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>5.170500000000001</v>
+        <v>5.1784</v>
       </c>
       <c r="E27" t="n">
-        <v>3.891099999999999</v>
+        <v>3.7293</v>
       </c>
       <c r="F27" t="n">
-        <v>1.279199999999999</v>
+        <v>1.449</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02880000000000094</v>
+        <v>-0.01259999999999972</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.1236</v>
+        <v>-6.105100000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>6.0951</v>
+        <v>6.092499999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>10.4515</v>
+        <v>10.3701</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4332</v>
+        <v>4.385899999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>6.018300000000001</v>
+        <v>5.9841</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.4804</v>
+        <v>-10.3827</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.5569</v>
+        <v>-10.4911</v>
       </c>
       <c r="O27" t="n">
-        <v>0.07669999999999977</v>
+        <v>0.1083999999999997</v>
       </c>
       <c r="P27" t="n">
-        <v>1.136</v>
+        <v>1.1382</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.903</v>
+        <v>-15.9344</v>
       </c>
       <c r="R27" t="n">
-        <v>17.0392</v>
+        <v>17.0722</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.3255</v>
+        <v>-1.3234</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.2071</v>
+        <v>-2.2324</v>
       </c>
       <c r="U27" t="n">
-        <v>0.8817000000000003</v>
+        <v>0.9090999999999998</v>
       </c>
       <c r="V27" t="n">
-        <v>5.3889</v>
+        <v>5.3758</v>
       </c>
       <c r="W27" t="n">
-        <v>11.5501</v>
+        <v>11.5258</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.1615</v>
+        <v>-6.149999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104728_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104728_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.5256</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104728_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.149999999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
